--- a/AtchisonRegime/Outputs/Aust/ASX300_Consumer_Discretionary/df_regEquityReturns_ASX300_Consumer_Discretionary.xlsx
+++ b/AtchisonRegime/Outputs/Aust/ASX300_Consumer_Discretionary/df_regEquityReturns_ASX300_Consumer_Discretionary.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q301"/>
+  <dimension ref="A1:Q302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17002,7 +17002,7 @@
         <v>-0.9726698406613064</v>
       </c>
       <c r="C291" t="n">
-        <v>0.1460332201527155</v>
+        <v>0.1241894196525952</v>
       </c>
       <c r="D291" t="b">
         <v>0</v>
@@ -17059,7 +17059,7 @@
         <v>-0.930850647666511</v>
       </c>
       <c r="C292" t="n">
-        <v>0.2388191536463469</v>
+        <v>0.2339228301603335</v>
       </c>
       <c r="D292" t="b">
         <v>0</v>
@@ -17116,7 +17116,7 @@
         <v>-0.8890737992235942</v>
       </c>
       <c r="C293" t="n">
-        <v>0.2406013064670542</v>
+        <v>0.2370619522653315</v>
       </c>
       <c r="D293" t="b">
         <v>0</v>
@@ -17173,7 +17173,7 @@
         <v>-1.090435517906162</v>
       </c>
       <c r="C294" t="n">
-        <v>0.2007569734303624</v>
+        <v>0.1988546216055985</v>
       </c>
       <c r="D294" t="b">
         <v>0</v>
@@ -17230,7 +17230,7 @@
         <v>-1.28973601261699</v>
       </c>
       <c r="C295" t="n">
-        <v>0.1400914415231331</v>
+        <v>0.1425534339131948</v>
       </c>
       <c r="D295" t="b">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>-1.487030325470401</v>
       </c>
       <c r="C296" t="n">
-        <v>0.08697420027797154</v>
+        <v>0.0881118604449648</v>
       </c>
       <c r="D296" t="b">
         <v>0</v>
@@ -17344,7 +17344,7 @@
         <v>-1.508648286865362</v>
       </c>
       <c r="C297" t="n">
-        <v>0.04458779450515634</v>
+        <v>0.05049734109636209</v>
       </c>
       <c r="D297" t="b">
         <v>0</v>
@@ -17401,7 +17401,7 @@
         <v>-1.530614951002829</v>
       </c>
       <c r="C298" t="n">
-        <v>0.03030594341745388</v>
+        <v>0.05226649969174183</v>
       </c>
       <c r="D298" t="b">
         <v>0</v>
@@ -17458,7 +17458,7 @@
         <v>-1.552867908392353</v>
       </c>
       <c r="C299" t="n">
-        <v>0.04619714416039293</v>
+        <v>0.06685384186450997</v>
       </c>
       <c r="D299" t="b">
         <v>0</v>
@@ -17515,7 +17515,7 @@
         <v>-1.4620752903488</v>
       </c>
       <c r="C300" t="n">
-        <v>0.03127296425735279</v>
+        <v>0.0775006846619135</v>
       </c>
       <c r="D300" t="b">
         <v>0</v>
@@ -17569,10 +17569,10 @@
         <v>45747</v>
       </c>
       <c r="B301" t="n">
-        <v>-1.380584681996217</v>
+        <v>-1.383605099136776</v>
       </c>
       <c r="C301" t="n">
-        <v>0.04765921338260101</v>
+        <v>0.09199325928623918</v>
       </c>
       <c r="D301" t="b">
         <v>0</v>
@@ -17618,6 +17618,63 @@
         <v>369.9695313306705</v>
       </c>
       <c r="Q301" t="n">
+        <v>128.8295961179075</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B302" t="n">
+        <v>-1.312657793185081</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.08562355455682437</v>
+      </c>
+      <c r="D302" t="b">
+        <v>0</v>
+      </c>
+      <c r="E302" t="b">
+        <v>1</v>
+      </c>
+      <c r="F302" t="n">
+        <v>-6.189814370079779</v>
+      </c>
+      <c r="G302" t="n">
+        <v>256720.5250874098</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0</v>
+      </c>
+      <c r="L302" t="n">
+        <v>-6.189814370079779</v>
+      </c>
+      <c r="M302" t="n">
+        <v>0</v>
+      </c>
+      <c r="N302" t="n">
+        <v>46.7262336232597</v>
+      </c>
+      <c r="O302" t="n">
+        <v>130.5573236007461</v>
+      </c>
+      <c r="P302" t="n">
+        <v>347.0691041154478</v>
+      </c>
+      <c r="Q302" t="n">
         <v>128.8295961179075</v>
       </c>
     </row>
